--- a/List Bug.xlsx
+++ b/List Bug.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6c28d2b6f55809ab/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6c28d2b6f55809ab/Documents/GitHub/Testcase_OMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ADFAF68-628A-4E4B-9E9B-611552261091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42A5E04B-8690-49E0-961B-0D3072328709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
